--- a/appointment_forms/037_legal_consultation_appointment_checklist_form_template--appointment_forms.xlsx
+++ b/appointment_forms/037_legal_consultation_appointment_checklist_form_template--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1291,17 +1291,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>action_items_choices</t>
+          <t>reminders_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>remind_client</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Remind Client</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>remind_client</t>
+          <t>remind_attorneys</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remind Client</t>
+          <t>Remind Attorneys</t>
         </is>
       </c>
     </row>
@@ -1330,29 +1330,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>remind_attorneys</t>
+          <t>remind_both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remind Attorneys</t>
+          <t>Remind Both</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reminders_choices</t>
+          <t>follow_up_reminders_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>remind_both</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remind Both</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1381,29 +1381,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>follow_up_reminders_choices</t>
+          <t>meeting_outcome_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Text Message</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1432,29 +1432,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meeting_outcome_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1466,27 +1466,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
